--- a/ksoft/docs/records/Finance_Institution_(Portador)_Records.xlsx
+++ b/ksoft/docs/records/Finance_Institution_(Portador)_Records.xlsx
@@ -2351,13 +2351,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{65CAD669-BDB8-494A-B442-4B427DB9B76B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{217B38E9-5BEE-4B13-971E-22798D3873AE}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F1130AC1-590E-4F21-A5AA-80F9B8051436}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0898547A-617D-4155-8F35-F7CADD31FB55}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC60E563-2EC1-4AAD-888C-94CD79479395}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{504E1453-4B79-4337-A002-4A3E9BC97CDA}"/>
 </file>
--- a/ksoft/docs/records/Finance_Institution_(Portador)_Records.xlsx
+++ b/ksoft/docs/records/Finance_Institution_(Portador)_Records.xlsx
@@ -2351,13 +2351,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{217B38E9-5BEE-4B13-971E-22798D3873AE}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{65CAD669-BDB8-494A-B442-4B427DB9B76B}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0898547A-617D-4155-8F35-F7CADD31FB55}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F1130AC1-590E-4F21-A5AA-80F9B8051436}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{504E1453-4B79-4337-A002-4A3E9BC97CDA}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC60E563-2EC1-4AAD-888C-94CD79479395}"/>
 </file>